--- a/estadistica2/data/blasquez_valdes.xlsx
+++ b/estadistica2/data/blasquez_valdes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCB840F-2C7E-9742-83B0-2821C7EB3C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E352175-DAE6-604A-9406-EB39E50B7563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="16">
   <si>
     <t>eleccion</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t>edad</t>
+  </si>
+  <si>
+    <t>p_votos</t>
   </si>
   <si>
     <t>experiencia</t>
@@ -62,7 +65,10 @@
     <t>Edad del legislador al momento de la elección</t>
   </si>
   <si>
-    <t>Años de experiencia previa en política (0 a 30)</t>
+    <t>Porcentaje de votos obtenidos por el legislador en su elección (%)</t>
+  </si>
+  <si>
+    <t>Años de experiencia política previa</t>
   </si>
 </sst>
 </file>
@@ -430,17 +436,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,10 +455,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0.55132895708084106</v>
@@ -471,12 +473,15 @@
         <v>45</v>
       </c>
       <c r="E2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>51.46</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0.94717293977737427</v>
@@ -488,12 +493,15 @@
         <v>67</v>
       </c>
       <c r="E3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>40.369999999999997</v>
+      </c>
+      <c r="F3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1.473332345485687</v>
@@ -505,12 +513,15 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>33.770000000000003</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0.55288344621658325</v>
@@ -522,12 +533,15 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>56.56</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>0.6786733865737915</v>
@@ -539,12 +553,15 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>45.26</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>2.9265567660331731</v>
@@ -556,12 +573,15 @@
         <v>64</v>
       </c>
       <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>3.3720007538795471</v>
@@ -573,12 +593,15 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>0.88460683822631836</v>
@@ -590,12 +613,15 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>46.15</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>2.4307882785797119</v>
@@ -607,12 +633,15 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="F10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>8.7813007831573486</v>
@@ -624,12 +653,15 @@
         <v>52</v>
       </c>
       <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>4.5350267365574837</v>
@@ -641,12 +673,15 @@
         <v>41</v>
       </c>
       <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>0.73778986930847168</v>
@@ -658,12 +693,15 @@
         <v>59</v>
       </c>
       <c r="E13">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>42.92</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>0.73242396116256714</v>
@@ -675,12 +713,15 @@
         <v>55</v>
       </c>
       <c r="E14">
+        <v>46.56</v>
+      </c>
+      <c r="F14">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>0.950583815574646</v>
@@ -692,12 +733,15 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>31.42</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>1.0945519804954531</v>
@@ -709,12 +753,15 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>29.48</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>2.3218637704849239</v>
@@ -726,12 +773,15 @@
         <v>58</v>
       </c>
       <c r="E17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>10.75</v>
+      </c>
+      <c r="F17">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>3.624391108751297</v>
@@ -743,12 +793,15 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>8.793451189994812</v>
@@ -760,12 +813,15 @@
         <v>49</v>
       </c>
       <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>0.96526443958282471</v>
@@ -777,12 +833,15 @@
         <v>41</v>
       </c>
       <c r="E20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>36.15</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>0.46641528606414789</v>
@@ -794,12 +853,15 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>43.61</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22">
         <v>0.70087820291519165</v>
@@ -811,12 +873,15 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>53.31</v>
+      </c>
+      <c r="F22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23">
         <v>1.0816329717636111</v>
@@ -828,12 +893,15 @@
         <v>63</v>
       </c>
       <c r="E23">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>37.24</v>
+      </c>
+      <c r="F23">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24">
         <v>1.32567435503006</v>
@@ -845,12 +913,15 @@
         <v>51</v>
       </c>
       <c r="E24">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>33.82</v>
+      </c>
+      <c r="F24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25">
         <v>0.57149112224578857</v>
@@ -862,12 +933,15 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>41.45</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26">
         <v>4.3371690809726724</v>
@@ -879,12 +953,15 @@
         <v>52</v>
       </c>
       <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27">
         <v>0.82552284002304077</v>
@@ -896,12 +973,15 @@
         <v>48</v>
       </c>
       <c r="E27">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44.04</v>
+      </c>
+      <c r="F27">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28">
         <v>2.310711145401001</v>
@@ -913,12 +993,15 @@
         <v>58</v>
       </c>
       <c r="E28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="F28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>2.6822952926158909</v>
@@ -930,12 +1013,15 @@
         <v>56</v>
       </c>
       <c r="E29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>8.23</v>
+      </c>
+      <c r="F29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30">
         <v>2.7929824590682979</v>
@@ -947,12 +1033,15 @@
         <v>32</v>
       </c>
       <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>0.57527720928192139</v>
@@ -964,12 +1053,15 @@
         <v>46</v>
       </c>
       <c r="E31">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>47.04</v>
+      </c>
+      <c r="F31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>0.50843179225921631</v>
@@ -981,12 +1073,15 @@
         <v>32</v>
       </c>
       <c r="E32">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+        <v>46.82</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33">
         <v>0.45897394418716431</v>
@@ -998,12 +1093,15 @@
         <v>53</v>
       </c>
       <c r="E33">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <v>60.08</v>
+      </c>
+      <c r="F33">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34">
         <v>1.071306467056274</v>
@@ -1015,12 +1113,15 @@
         <v>53</v>
       </c>
       <c r="E34">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38.51</v>
+      </c>
+      <c r="F34">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35">
         <v>0.32599776983261108</v>
@@ -1032,12 +1133,15 @@
         <v>41</v>
       </c>
       <c r="E35">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+        <v>48.19</v>
+      </c>
+      <c r="F35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>1.3677757978439331</v>
@@ -1049,12 +1153,15 @@
         <v>33</v>
       </c>
       <c r="E36">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>36.76</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37">
         <v>1.0334992408752439</v>
@@ -1066,12 +1173,15 @@
         <v>52</v>
       </c>
       <c r="E37">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>33.229999999999997</v>
+      </c>
+      <c r="F37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38">
         <v>7.4546906352043152</v>
@@ -1083,12 +1193,15 @@
         <v>49</v>
       </c>
       <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39">
         <v>0.58638662099838257</v>
@@ -1100,12 +1213,15 @@
         <v>33</v>
       </c>
       <c r="E39">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38.47</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>1.7988824844360349</v>
@@ -1117,12 +1233,15 @@
         <v>36</v>
       </c>
       <c r="E40">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>17.38</v>
+      </c>
+      <c r="F40">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41">
         <v>1.991430819034576</v>
@@ -1134,12 +1253,15 @@
         <v>30</v>
       </c>
       <c r="E41">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+        <v>21.16</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42">
         <v>8.6308878660202026</v>
@@ -1151,12 +1273,15 @@
         <v>46</v>
       </c>
       <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43">
         <v>2.9424870014190669</v>
@@ -1168,12 +1293,15 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44">
         <v>2.9724526405334468</v>
@@ -1185,12 +1313,15 @@
         <v>47</v>
       </c>
       <c r="E44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45">
         <v>0.45218557119369512</v>
@@ -1202,12 +1333,15 @@
         <v>31</v>
       </c>
       <c r="E45">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+        <v>49.45</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B46">
         <v>0.48136442899703979</v>
@@ -1219,12 +1353,15 @@
         <v>37</v>
       </c>
       <c r="E46">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+        <v>42.98</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47">
         <v>2.4516201019287109</v>
@@ -1236,12 +1373,15 @@
         <v>41</v>
       </c>
       <c r="E47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+        <v>7.37</v>
+      </c>
+      <c r="F47">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48">
         <v>7.1173812448978424</v>
@@ -1253,12 +1393,15 @@
         <v>34</v>
       </c>
       <c r="E48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F48">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49">
         <v>2.0628821849822998</v>
@@ -1270,12 +1413,15 @@
         <v>25</v>
       </c>
       <c r="E49">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+        <v>24.03</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B50">
         <v>6.3345716893672943</v>
@@ -1287,12 +1433,15 @@
         <v>50</v>
       </c>
       <c r="E50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B51">
         <v>0.82390129566192627</v>
@@ -1304,12 +1453,15 @@
         <v>51</v>
       </c>
       <c r="E51">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+        <v>34.71</v>
+      </c>
+      <c r="F51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B52">
         <v>0.80015242099761963</v>
@@ -1321,12 +1473,15 @@
         <v>60</v>
       </c>
       <c r="E52">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+        <v>45.62</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B53">
         <v>2.5735989212989812</v>
@@ -1338,12 +1493,15 @@
         <v>75</v>
       </c>
       <c r="E53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6.6</v>
+      </c>
+      <c r="F53">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54">
         <v>0.86343079805374146</v>
@@ -1355,12 +1513,15 @@
         <v>30</v>
       </c>
       <c r="E54">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+        <v>39.35</v>
+      </c>
+      <c r="F54">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B55">
         <v>1.550090610980988</v>
@@ -1372,12 +1533,15 @@
         <v>74</v>
       </c>
       <c r="E55">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+        <v>32.06</v>
+      </c>
+      <c r="F55">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B56">
         <v>0.92325001955032349</v>
@@ -1389,12 +1553,15 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+        <v>46.69</v>
+      </c>
+      <c r="F56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B57">
         <v>2.5774547457695012</v>
@@ -1406,12 +1573,15 @@
         <v>54</v>
       </c>
       <c r="E57">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13.11</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0.53918898105621338</v>
@@ -1423,12 +1593,15 @@
         <v>36</v>
       </c>
       <c r="E58">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+        <v>45.02</v>
+      </c>
+      <c r="F58">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B59">
         <v>2.1907022595405579</v>
@@ -1440,12 +1613,15 @@
         <v>54</v>
       </c>
       <c r="E59">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+        <v>14.64</v>
+      </c>
+      <c r="F59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60">
         <v>8.8844913244247437</v>
@@ -1457,12 +1633,15 @@
         <v>29</v>
       </c>
       <c r="E60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B61">
         <v>0.98431676626205444</v>
@@ -1474,12 +1653,15 @@
         <v>35</v>
       </c>
       <c r="E61">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+        <v>45.19</v>
+      </c>
+      <c r="F61">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B62">
         <v>2.472334206104279</v>
@@ -1491,12 +1673,15 @@
         <v>50</v>
       </c>
       <c r="E62">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+        <v>8.16</v>
+      </c>
+      <c r="F62">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63">
         <v>2.2935831546783452</v>
@@ -1508,12 +1693,15 @@
         <v>55</v>
       </c>
       <c r="E63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13.2</v>
+      </c>
+      <c r="F63">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B64">
         <v>1.1460974812507629</v>
@@ -1525,12 +1713,15 @@
         <v>37</v>
       </c>
       <c r="E64">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+        <v>31.55</v>
+      </c>
+      <c r="F64">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B65">
         <v>0.60072779655456543</v>
@@ -1542,12 +1733,15 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B66">
         <v>0.52340298891067505</v>
@@ -1559,12 +1753,15 @@
         <v>30</v>
       </c>
       <c r="E66">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+        <v>53.59</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B67">
         <v>9.1988146305084229</v>
@@ -1576,12 +1773,15 @@
         <v>39</v>
       </c>
       <c r="E67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B68">
         <v>0.56646913290023804</v>
@@ -1593,12 +1793,15 @@
         <v>64</v>
       </c>
       <c r="E68">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+        <v>48.31</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B69">
         <v>0.85150361061096191</v>
@@ -1610,12 +1813,15 @@
         <v>34</v>
       </c>
       <c r="E69">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+        <v>47.99</v>
+      </c>
+      <c r="F69">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B70">
         <v>6.7378564178943634</v>
@@ -1627,12 +1833,15 @@
         <v>33</v>
       </c>
       <c r="E70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B71">
         <v>0.65803617238998413</v>
@@ -1644,12 +1853,15 @@
         <v>37</v>
       </c>
       <c r="E71">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+        <v>43.61</v>
+      </c>
+      <c r="F71">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B72">
         <v>4.2413432896137238</v>
@@ -1661,12 +1873,15 @@
         <v>70</v>
       </c>
       <c r="E72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F72">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B73">
         <v>0.73643267154693604</v>
@@ -1678,12 +1893,15 @@
         <v>36</v>
       </c>
       <c r="E73">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+        <v>52.96</v>
+      </c>
+      <c r="F73">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B74">
         <v>1.5644174814224241</v>
@@ -1695,12 +1913,15 @@
         <v>65</v>
       </c>
       <c r="E74">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+        <v>28.53</v>
+      </c>
+      <c r="F74">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B75">
         <v>3.3145049214363098</v>
@@ -1712,12 +1933,15 @@
         <v>33</v>
       </c>
       <c r="E75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B76">
         <v>8.5119950771331787</v>
@@ -1729,12 +1953,15 @@
         <v>67</v>
       </c>
       <c r="E76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F76">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B77">
         <v>0.78810751438140869</v>
@@ -1746,12 +1973,15 @@
         <v>58</v>
       </c>
       <c r="E77">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+        <v>48.35</v>
+      </c>
+      <c r="F77">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B78">
         <v>2.8352455794811249</v>
@@ -1763,12 +1993,15 @@
         <v>24</v>
       </c>
       <c r="E78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B79">
         <v>6.9268320500850677</v>
@@ -1780,12 +2013,15 @@
         <v>43</v>
       </c>
       <c r="E79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F79">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B80">
         <v>7.1280349791049957</v>
@@ -1797,12 +2033,15 @@
         <v>33</v>
       </c>
       <c r="E80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F80">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B81">
         <v>1.821643710136414</v>
@@ -1814,12 +2053,15 @@
         <v>40</v>
       </c>
       <c r="E81">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13.63</v>
+      </c>
+      <c r="F81">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B82">
         <v>4.4510594010353088</v>
@@ -1831,12 +2073,15 @@
         <v>44</v>
       </c>
       <c r="E82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F82">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B83">
         <v>7.0027497410774231</v>
@@ -1848,12 +2093,15 @@
         <v>60</v>
       </c>
       <c r="E83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F83">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B84">
         <v>0.53154468536376953</v>
@@ -1865,12 +2113,15 @@
         <v>29</v>
       </c>
       <c r="E84">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+        <v>56.76</v>
+      </c>
+      <c r="F84">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B85">
         <v>2.1966788172721858</v>
@@ -1882,12 +2133,15 @@
         <v>38</v>
       </c>
       <c r="E85">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13.48</v>
+      </c>
+      <c r="F85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B86">
         <v>8.6344221234321594</v>
@@ -1899,12 +2153,15 @@
         <v>65</v>
       </c>
       <c r="E86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F86">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B87">
         <v>0.55335193872451782</v>
@@ -1916,12 +2173,15 @@
         <v>41</v>
       </c>
       <c r="E87">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+        <v>46.42</v>
+      </c>
+      <c r="F87">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B88">
         <v>2.7871382236480708</v>
@@ -1933,12 +2193,15 @@
         <v>49</v>
       </c>
       <c r="E88">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+        <v>8.83</v>
+      </c>
+      <c r="F88">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B89">
         <v>0.70146381855010986</v>
@@ -1950,12 +2213,15 @@
         <v>65</v>
       </c>
       <c r="E89">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+        <v>47.61</v>
+      </c>
+      <c r="F89">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B90">
         <v>1.134470999240875</v>
@@ -1967,12 +2233,15 @@
         <v>39</v>
       </c>
       <c r="E90">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+        <v>34.659999999999997</v>
+      </c>
+      <c r="F90">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B91">
         <v>0.95171481370925903</v>
@@ -1984,12 +2253,15 @@
         <v>21</v>
       </c>
       <c r="E91">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+        <v>43.53</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B92">
         <v>1.2705323100090029</v>
@@ -2001,12 +2273,15 @@
         <v>58</v>
       </c>
       <c r="E92">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+        <v>35.07</v>
+      </c>
+      <c r="F92">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B93">
         <v>0.49916237592697138</v>
@@ -2018,12 +2293,15 @@
         <v>35</v>
       </c>
       <c r="E93">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+        <v>54.86</v>
+      </c>
+      <c r="F93">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B94">
         <v>5.0061953667318448</v>
@@ -2035,12 +2313,15 @@
         <v>48</v>
       </c>
       <c r="E94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F94">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B95">
         <v>0.43170630931854248</v>
@@ -2052,12 +2333,15 @@
         <v>49</v>
       </c>
       <c r="E95">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+        <v>49.73</v>
+      </c>
+      <c r="F95">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B96">
         <v>0.94278931617736816</v>
@@ -2069,12 +2353,15 @@
         <v>41</v>
       </c>
       <c r="E96">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+        <v>39.18</v>
+      </c>
+      <c r="F96">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B97">
         <v>4.1798034310340881</v>
@@ -2086,12 +2373,15 @@
         <v>67</v>
       </c>
       <c r="E97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F97">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B98">
         <v>0.88893294334411621</v>
@@ -2103,12 +2393,15 @@
         <v>39</v>
       </c>
       <c r="E98">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+        <v>43.7</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B99">
         <v>0.83915680646896362</v>
@@ -2120,12 +2413,15 @@
         <v>41</v>
       </c>
       <c r="E99">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44.52</v>
+      </c>
+      <c r="F99">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B100">
         <v>0.49812883138656622</v>
@@ -2137,12 +2433,15 @@
         <v>45</v>
       </c>
       <c r="E100">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+        <v>50.06</v>
+      </c>
+      <c r="F100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B101">
         <v>3.321561217308044</v>
@@ -2154,12 +2453,15 @@
         <v>34</v>
       </c>
       <c r="E101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F101">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B102">
         <v>2.85266324877739</v>
@@ -2171,12 +2473,15 @@
         <v>34</v>
       </c>
       <c r="E102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B103">
         <v>2.8748157620429988</v>
@@ -2188,12 +2493,15 @@
         <v>40</v>
       </c>
       <c r="E103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F103">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B104">
         <v>8.5126641392707825</v>
@@ -2205,12 +2513,15 @@
         <v>81</v>
       </c>
       <c r="E104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F104">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B105">
         <v>0.94347059726715088</v>
@@ -2222,12 +2533,15 @@
         <v>29</v>
       </c>
       <c r="E105">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+        <v>37.119999999999997</v>
+      </c>
+      <c r="F105">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B106">
         <v>3.206231147050858</v>
@@ -2239,12 +2553,15 @@
         <v>30</v>
       </c>
       <c r="E106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B107">
         <v>0.85048139095306396</v>
@@ -2256,12 +2573,15 @@
         <v>48</v>
       </c>
       <c r="E107">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+        <v>45.01</v>
+      </c>
+      <c r="F107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B108">
         <v>1.998969614505768</v>
@@ -2273,12 +2593,15 @@
         <v>56</v>
       </c>
       <c r="E108">
+        <v>29.45</v>
+      </c>
+      <c r="F108">
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B109">
         <v>6.9920456409454346</v>
@@ -2290,12 +2613,15 @@
         <v>58</v>
       </c>
       <c r="E109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F109">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B110">
         <v>6.6965921223163596</v>
@@ -2307,12 +2633,15 @@
         <v>51</v>
       </c>
       <c r="E110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F110">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B111">
         <v>2.5068888068199162</v>
@@ -2324,12 +2653,15 @@
         <v>38</v>
       </c>
       <c r="E111">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+        <v>9.49</v>
+      </c>
+      <c r="F111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112">
         <v>8.9737996459007263</v>
@@ -2341,12 +2673,15 @@
         <v>78</v>
       </c>
       <c r="E112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F112">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B113">
         <v>0.99864751100540161</v>
@@ -2358,12 +2693,15 @@
         <v>54</v>
       </c>
       <c r="E113">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+        <v>39.89</v>
+      </c>
+      <c r="F113">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B114">
         <v>0.89784294366836548</v>
@@ -2375,12 +2713,15 @@
         <v>36</v>
       </c>
       <c r="E114">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+        <v>42.34</v>
+      </c>
+      <c r="F114">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B115">
         <v>0.85201412439346313</v>
@@ -2392,12 +2733,15 @@
         <v>44</v>
       </c>
       <c r="E115">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+        <v>55.28</v>
+      </c>
+      <c r="F115">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B116">
         <v>6.669166088104248</v>
@@ -2409,12 +2753,15 @@
         <v>52</v>
       </c>
       <c r="E116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F116">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B117">
         <v>2.2306844592094421</v>
@@ -2426,12 +2773,15 @@
         <v>41</v>
       </c>
       <c r="E117">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+        <v>16.89</v>
+      </c>
+      <c r="F117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B118">
         <v>2.7597720921039581</v>
@@ -2443,12 +2793,15 @@
         <v>32</v>
       </c>
       <c r="E118">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B119">
         <v>1.916381418704987</v>
@@ -2460,12 +2813,15 @@
         <v>31</v>
       </c>
       <c r="E119">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15.83</v>
+      </c>
+      <c r="F119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B120">
         <v>7.2938536107540131</v>
@@ -2477,12 +2833,15 @@
         <v>48</v>
       </c>
       <c r="E120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F120">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B121">
         <v>0.51383852958679199</v>
@@ -2494,12 +2853,15 @@
         <v>36</v>
       </c>
       <c r="E121">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+        <v>53.48</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B122">
         <v>1.9898402690887449</v>
@@ -2511,12 +2873,15 @@
         <v>40</v>
       </c>
       <c r="E122">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+        <v>24.16</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B123">
         <v>2.1108382940292358</v>
@@ -2528,12 +2893,15 @@
         <v>50</v>
       </c>
       <c r="E123">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13.24</v>
+      </c>
+      <c r="F123">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B124">
         <v>8.5359621047973633</v>
@@ -2545,12 +2913,15 @@
         <v>39</v>
       </c>
       <c r="E124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B125">
         <v>1.0441097617149351</v>
@@ -2562,12 +2933,15 @@
         <v>38</v>
       </c>
       <c r="E125">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+        <v>32.11</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B126">
         <v>1.8352949619293211</v>
@@ -2579,12 +2953,15 @@
         <v>35</v>
       </c>
       <c r="E126">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+        <v>26.23</v>
+      </c>
+      <c r="F126">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B127">
         <v>3.747019916772842</v>
@@ -2596,12 +2973,15 @@
         <v>47</v>
       </c>
       <c r="E127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F127">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B128">
         <v>8.664318323135376</v>
@@ -2613,12 +2993,15 @@
         <v>54</v>
       </c>
       <c r="E128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F128">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B129">
         <v>7.4384976923465729</v>
@@ -2630,12 +3013,15 @@
         <v>68</v>
       </c>
       <c r="E129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F129">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B130">
         <v>2.4920099973678589</v>
@@ -2647,12 +3033,15 @@
         <v>51</v>
       </c>
       <c r="E130">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+        <v>10.66</v>
+      </c>
+      <c r="F130">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B131">
         <v>9.1481310129165649</v>
@@ -2664,12 +3053,15 @@
         <v>54</v>
       </c>
       <c r="E131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B132">
         <v>5.5579743161797523</v>
@@ -2681,12 +3073,15 @@
         <v>75</v>
       </c>
       <c r="E132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F132">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B133">
         <v>9.2073208093643188</v>
@@ -2698,12 +3093,15 @@
         <v>42</v>
       </c>
       <c r="E133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F133">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B134">
         <v>9.4806435704231262</v>
@@ -2715,12 +3113,15 @@
         <v>48</v>
       </c>
       <c r="E134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F134">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B135">
         <v>9.5600199699401855</v>
@@ -2732,12 +3133,15 @@
         <v>42</v>
       </c>
       <c r="E135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F135">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B136">
         <v>0.83545953035354614</v>
@@ -2749,12 +3153,15 @@
         <v>38</v>
       </c>
       <c r="E136">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38.69</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B137">
         <v>3.270387202501297</v>
@@ -2766,12 +3173,15 @@
         <v>32</v>
       </c>
       <c r="E137">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B138">
         <v>8.5253837704658508</v>
@@ -2783,12 +3193,15 @@
         <v>38</v>
       </c>
       <c r="E138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F138">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B139">
         <v>8.5237014293670654</v>
@@ -2800,12 +3213,15 @@
         <v>25</v>
       </c>
       <c r="E139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F139">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B140">
         <v>1.937081515789032</v>
@@ -2817,12 +3233,15 @@
         <v>62</v>
       </c>
       <c r="E140">
+        <v>25.33</v>
+      </c>
+      <c r="F140">
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B141">
         <v>3.2135401666164398</v>
@@ -2834,12 +3253,15 @@
         <v>69</v>
       </c>
       <c r="E141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F141">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B142">
         <v>2.4352112412452702</v>
@@ -2851,12 +3273,15 @@
         <v>32</v>
       </c>
       <c r="E142">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12.43</v>
+      </c>
+      <c r="F142">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B143">
         <v>2.699415534734726</v>
@@ -2868,12 +3293,15 @@
         <v>48</v>
       </c>
       <c r="E143">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12.55</v>
+      </c>
+      <c r="F143">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B144">
         <v>3.4183989465236659</v>
@@ -2885,12 +3313,15 @@
         <v>51</v>
       </c>
       <c r="E144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F144">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B145">
         <v>7.1917940676212311</v>
@@ -2902,12 +3333,15 @@
         <v>46</v>
       </c>
       <c r="E145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F145">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B146">
         <v>2.0770531892776489</v>
@@ -2919,12 +3353,15 @@
         <v>34</v>
       </c>
       <c r="E146">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="F146">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B147">
         <v>9.1212952136993408</v>
@@ -2936,12 +3373,15 @@
         <v>42</v>
       </c>
       <c r="E147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F147">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B148">
         <v>7.2870290279388428</v>
@@ -2953,12 +3393,15 @@
         <v>56</v>
       </c>
       <c r="E148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F148">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B149">
         <v>9.362635612487793</v>
@@ -2970,12 +3413,15 @@
         <v>35</v>
       </c>
       <c r="E149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F149">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B150">
         <v>4.4069846346974373</v>
@@ -2987,12 +3433,15 @@
         <v>76</v>
       </c>
       <c r="E150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F150">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B151">
         <v>7.2523204982280731</v>
@@ -3004,12 +3453,15 @@
         <v>34</v>
       </c>
       <c r="E151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F151">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B152">
         <v>8.5408037900924683</v>
@@ -3021,12 +3473,15 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F152">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B153">
         <v>3.3547639846801758</v>
@@ -3038,12 +3493,15 @@
         <v>52</v>
       </c>
       <c r="E153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F153">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B154">
         <v>8.7218740582466125</v>
@@ -3055,12 +3513,15 @@
         <v>38</v>
       </c>
       <c r="E154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F154">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B155">
         <v>3.3809244632720952</v>
@@ -3072,12 +3533,15 @@
         <v>37</v>
       </c>
       <c r="E155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="F155">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B156">
         <v>2.484519779682159</v>
@@ -3089,7 +3553,10 @@
         <v>44</v>
       </c>
       <c r="E156">
-        <v>6</v>
+        <v>11.77</v>
+      </c>
+      <c r="F156">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3099,19 +3566,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3119,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3127,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -3135,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -3143,7 +3610,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -3151,7 +3618,15 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/estadistica2/data/blasquez_valdes.xlsx
+++ b/estadistica2/data/blasquez_valdes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E352175-DAE6-604A-9406-EB39E50B7563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B04284E-09E5-3646-A0DC-408A4AD7308E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
